--- a/candidatures.xlsx
+++ b/candidatures.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="30">
   <si>
     <t>Date</t>
   </si>
@@ -71,6 +71,36 @@
   </si>
   <si>
     <t>11/04/2026 19:01:47</t>
+  </si>
+  <si>
+    <t>12/04/2026 15:26:14</t>
+  </si>
+  <si>
+    <t>Regnology</t>
+  </si>
+  <si>
+    <t>Software Engineer, Tunis</t>
+  </si>
+  <si>
+    <t>haytham.benhamed@regnum.fr</t>
+  </si>
+  <si>
+    <t>12/04/2026 15:36:18</t>
+  </si>
+  <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>12/04/2026 15:38:19</t>
+  </si>
+  <si>
+    <t>Exemple Entreprise</t>
+  </si>
+  <si>
+    <t>Titre de l'emploi</t>
+  </si>
+  <si>
+    <t>exemple@example.com</t>
   </si>
 </sst>
 </file>
@@ -451,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -647,6 +677,57 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/candidatures.xlsx
+++ b/candidatures.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
@@ -101,6 +101,18 @@
   </si>
   <si>
     <t>exemple@example.com</t>
+  </si>
+  <si>
+    <t>16/04/2026 19:06:03</t>
+  </si>
+  <si>
+    <t>UMANLINK GROUP</t>
+  </si>
+  <si>
+    <t>Développeur Senior Java</t>
+  </si>
+  <si>
+    <t>career@umanlink-group.com</t>
   </si>
 </sst>
 </file>
@@ -481,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -728,6 +740,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
